--- a/reference/input/reference.xlsx
+++ b/reference/input/reference.xlsx
@@ -3584,7 +3584,7 @@
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>Captures a time-aligned media transcript (subtitles, captions, or diarized speech). The body is a sequence of cue blocks, each introduced by a `&lt;bdiv&gt;` delimiter; a non-empty `&lt;track&gt;` body must begin with a `&lt;bdiv&gt;`. A cue block carries a mandatory start time, an optional end time (each a run of `&lt;hours&gt;`/`&lt;minutes&gt;`/`&lt;seconds&gt;`/`&lt;msecs&gt;`), an optional `&lt;frame&gt;`, an optional `&lt;audio&gt;`, and an optional transcript of `&lt;voice&gt;`-attributed turns.</t>
+          <t>Captures a time-aligned media transcript (subtitles, captions, or diarized speech). The body may open with a single `&lt;cover&gt;` (a track-wide image), then a sequence of cue blocks, each introduced by a `&lt;bdiv&gt;` delimiter; a non-empty `&lt;track&gt;` body must begin with a `&lt;cover&gt;` or a `&lt;bdiv&gt;`. A cue block carries a mandatory start time, an optional end time (each a run of `&lt;hours&gt;`/`&lt;minutes&gt;`/`&lt;seconds&gt;`/`&lt;msecs&gt;`), an optional `&lt;chapter&gt;`, an optional `&lt;frame&gt;`, an optional `&lt;audio&gt;`, and an optional transcript of `&lt;voice&gt;`-attributed turns.</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Only `&lt;frame&gt;`, `&lt;audio&gt;`, and `&lt;voice&gt;`, within cue blocks</t>
+          <t>`&lt;cover&gt;` before the first cue block; within cue blocks, `&lt;chapter&gt;`, `&lt;frame&gt;`, `&lt;audio&gt;`, and `&lt;voice&gt;`</t>
         </is>
       </c>
       <c r="I78" t="b">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>A representative image for a `&lt;track&gt;` as a whole — podcast artwork, a poster, a title card. Appears once, before the first cue block. Same shape as `&lt;frame&gt;`: an optional element head followed by an optional `&lt;src&gt;`.</t>
+          <t>A representative image for a `&lt;track&gt;` as a whole — for example podcast artwork, a poster, or a title card. Appears once, before the first cue block. Same shape as `&lt;frame&gt;`: an optional element head followed by an optional `&lt;src&gt;`.</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">

--- a/reference/input/reference.xlsx
+++ b/reference/input/reference.xlsx
@@ -620,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="20" defaultRowHeight="16"/>
   <cols>
     <col width="27.1640625" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>`&lt;timestamp&gt;`</t>
+          <t>`&lt;layer&gt;`</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>TBD. Needed, if the individual hour/minute/etc are not all required (else cannot unambiguously interpret `&lt;hour&gt;0&lt;/hour&gt;&lt;minute&gt;2&lt;/minute&gt;&lt;second&gt;3&lt;/second&gt;`)</t>
+          <t>The conceptual layer of the host element in the document.</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="E35" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" s="6" t="b">
         <v>0</v>
@@ -1953,46 +1953,42 @@
         <v>0</v>
       </c>
       <c r="I35" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J35" s="1" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>[03a] property (outer)</t>
+          <t>[03b] property (inner)</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>`&lt;layer&gt;`</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>The conceptual layer of the host element in the document.</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>Can only be part of the [element head](#element-head) of a semantic element.</t>
+          <t>`&lt;summary&gt;`</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Can only be child of `&lt;meta&gt;`.</t>
         </is>
       </c>
       <c r="E36" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G36" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I36" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2004,23 +2000,23 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>`&lt;hour&gt;`</t>
+          <t>`&lt;classification&gt;`</t>
         </is>
       </c>
       <c r="C37" s="5" t="n"/>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>Can only be child of a semantic element.</t>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Can only be child of `&lt;meta&gt;`.</t>
         </is>
       </c>
       <c r="E37" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G37" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="1" t="b">
         <v>0</v>
@@ -2035,18 +2031,22 @@
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>[03b] property (inner)</t>
+          <t>[04] payload</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>`&lt;minute&gt;`</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>Can only be child of a semantic element.</t>
+          <t>`&lt;src&gt;`</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>The image's source.</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Can only be part of the picture-specific element body sequence of `&lt;picture&gt;`.</t>
         </is>
       </c>
       <c r="E38" s="6" t="b">
@@ -2060,65 +2060,66 @@
       </c>
       <c r="H38" s="1" t="b">
         <v>0</v>
-      </c>
-      <c r="I38" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="J38" s="1" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="39" ht="17" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>[03b] property (inner)</t>
+          <t>[04] payload</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>`&lt;second&gt;`</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="n"/>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>Can only be child of a semantic element.</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="F39" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G39" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I39" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="J39" s="1" t="b">
-        <v>1</v>
-      </c>
+          <t>`&lt;tabular&gt;`</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Structured tabular data. Uses the same cell model as `&lt;table&gt;`, but without an element head of its own.</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Can only be part of the picture-specific element body sequence of [`&lt;picture class="chart"&gt;`](#picture).</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>Only on cell level, in case of virtual `&lt;text&gt;`</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>Only on cell level, in case of virtual `&lt;text&gt;`</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I39" s="10" t="n"/>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>[03b] property (inner)</t>
+          <t>[04] payload</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>`&lt;centisecond&gt;`</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="n"/>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>Can only be child of a semantic element.</t>
+          <t>`&lt;checkbox&gt;`</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Empty element representing checkbox selection state.</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Any context that allows raw text content.</t>
         </is>
       </c>
       <c r="E40" s="6" t="b">
@@ -2132,29 +2133,27 @@
       </c>
       <c r="H40" s="1" t="b">
         <v>0</v>
-      </c>
-      <c r="I40" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="J40" s="1" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>[03b] property (inner)</t>
+          <t>[04] payload</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>`&lt;summary&gt;`</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="n"/>
+          <t>`&lt;content&gt;`</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Whitespace-preserving text container. Retains all whitespace within the element (equivalent to `xml:space="preserve"`), enabling use in whitespace-sensitive scenarios such as code blocks. XML special characters may alternatively be conveyed via CDATA.</t>
+        </is>
+      </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Can only be child of `&lt;meta&gt;`.</t>
+          <t>Any context that allows raw text content.</t>
         </is>
       </c>
       <c r="E41" s="6" t="b">
@@ -2168,29 +2167,27 @@
       </c>
       <c r="H41" s="1" t="b">
         <v>0</v>
-      </c>
-      <c r="I41" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="J41" s="1" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="42" ht="17" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>[03b] property (inner)</t>
+          <t>[05] formatting</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>`&lt;classification&gt;`</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="n"/>
+          <t>`&lt;bold&gt;`</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Indicates bold formatting.</t>
+        </is>
+      </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Can only be child of `&lt;meta&gt;`.</t>
+          <t>Any context that allows raw text content.</t>
         </is>
       </c>
       <c r="E42" s="6" t="b">
@@ -2199,48 +2196,42 @@
       <c r="F42" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="G42" s="1" t="b">
+      <c r="G42" s="6" t="b">
         <v>1</v>
       </c>
       <c r="H42" s="1" t="b">
         <v>0</v>
-      </c>
-      <c r="I42" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="J42" s="1" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="43" ht="34" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>[04] payload</t>
+          <t>[05] formatting</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>`&lt;src&gt;`</t>
+          <t>`&lt;italic&gt;`</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>The image's source.</t>
+          <t>Indicates italic formatting.</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Can only be part of the picture-specific element body sequence of `&lt;picture&gt;`.</t>
+          <t>Any context that allows raw text content.</t>
         </is>
       </c>
       <c r="E43" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="G43" s="1" t="b">
-        <v>0</v>
+      <c r="G43" s="6" t="b">
+        <v>1</v>
       </c>
       <c r="H43" s="1" t="b">
         <v>0</v>
@@ -2249,56 +2240,51 @@
     <row r="44" ht="51" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>[04] payload</t>
+          <t>[05] formatting</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>`&lt;tabular&gt;`</t>
+          <t>`&lt;underline&gt;`</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Structured tabular data. Uses the same cell model as `&lt;table&gt;`, but without an element head of its own.</t>
+          <t>Indicates underlined formatting.</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Can only be part of the picture-specific element body sequence of [`&lt;picture class="chart"&gt;`](#picture).</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="F44" s="10" t="inlineStr">
-        <is>
-          <t>Only on cell level, in case of virtual `&lt;text&gt;`</t>
-        </is>
-      </c>
-      <c r="G44" s="10" t="inlineStr">
-        <is>
-          <t>Only on cell level, in case of virtual `&lt;text&gt;`</t>
-        </is>
-      </c>
-      <c r="H44" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I44" s="10" t="n"/>
+          <t>Any context that allows raw text content.</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G44" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H44" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="45" ht="17" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>[04] payload</t>
+          <t>[05] formatting</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>`&lt;checkbox&gt;`</t>
+          <t>`&lt;strikethrough&gt;`</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Empty element representing checkbox selection state.</t>
+          <t>Indicates struck-through formatting.</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -2307,13 +2293,13 @@
         </is>
       </c>
       <c r="E45" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="G45" s="1" t="b">
-        <v>0</v>
+      <c r="G45" s="6" t="b">
+        <v>1</v>
       </c>
       <c r="H45" s="1" t="b">
         <v>0</v>
@@ -2322,17 +2308,17 @@
     <row r="46" ht="17" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>[04] payload</t>
+          <t>[05] formatting</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>`&lt;content&gt;`</t>
+          <t>`&lt;superscript&gt;`</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Whitespace-preserving text container. Retains all whitespace within the element (equivalent to `xml:space="preserve"`), enabling use in whitespace-sensitive scenarios such as code blocks. XML special characters may alternatively be conveyed via CDATA.</t>
+          <t>Indicates superscript formatting.</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -2346,7 +2332,7 @@
       <c r="F46" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="G46" s="1" t="b">
+      <c r="G46" s="6" t="b">
         <v>1</v>
       </c>
       <c r="H46" s="1" t="b">
@@ -2361,12 +2347,12 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>`&lt;bold&gt;`</t>
+          <t>`&lt;subscript&gt;`</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Indicates bold formatting.</t>
+          <t>Indicates subscript formatting.</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -2395,12 +2381,12 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>`&lt;italic&gt;`</t>
+          <t>`&lt;handwriting&gt;`</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Indicates italic formatting.</t>
+          <t>Indicates handwritten text.</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -2429,12 +2415,12 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>`&lt;underline&gt;`</t>
+          <t>`&lt;rtl&gt;`</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Indicates underlined formatting.</t>
+          <t>Indicates right-to-left direction.</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -2458,32 +2444,32 @@
     <row r="50" ht="17" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>[05] formatting</t>
+          <t>[06] structural</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>`&lt;strikethrough&gt;`</t>
+          <t>`&lt;fcel&gt;`</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Indicates struck-through formatting.</t>
+          <t>Indicates the beginning of a full / regular cell.</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Any context that allows raw text content.</t>
+          <t>Can only be child of `&lt;table&gt;`, `&lt;index&gt;`, or `&lt;tabular&gt;`</t>
         </is>
       </c>
       <c r="E50" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="G50" s="6" t="b">
-        <v>1</v>
+      <c r="G50" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="H50" s="1" t="b">
         <v>0</v>
@@ -2492,32 +2478,32 @@
     <row r="51" ht="17" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>[05] formatting</t>
+          <t>[06] structural</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>`&lt;superscript&gt;`</t>
+          <t>`&lt;ecel&gt;`</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Indicates superscript formatting.</t>
+          <t>Indicates the beginning of an empty cell.</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Any context that allows raw text content.</t>
+          <t>Can only be child of `&lt;table&gt;`, `&lt;index&gt;`, or `&lt;tabular&gt;`</t>
         </is>
       </c>
       <c r="E51" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="G51" s="6" t="b">
-        <v>1</v>
+      <c r="G51" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="H51" s="1" t="b">
         <v>0</v>
@@ -2526,32 +2512,32 @@
     <row r="52" ht="17" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>[05] formatting</t>
+          <t>[06] structural</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>`&lt;subscript&gt;`</t>
+          <t>`&lt;ched&gt;`</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Indicates subscript formatting.</t>
+          <t>Indicates the beginning of a column header cell.</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Any context that allows raw text content.</t>
+          <t>Can only be child of `&lt;table&gt;`, `&lt;index&gt;`, or `&lt;tabular&gt;`</t>
         </is>
       </c>
       <c r="E52" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="G52" s="6" t="b">
-        <v>1</v>
+      <c r="G52" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="H52" s="1" t="b">
         <v>0</v>
@@ -2560,32 +2546,32 @@
     <row r="53" ht="17" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>[05] formatting</t>
+          <t>[06] structural</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>`&lt;handwriting&gt;`</t>
+          <t>`&lt;rhed&gt;`</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Indicates handwritten text.</t>
+          <t>Indicates the beginning of a row header cell.</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Any context that allows raw text content.</t>
+          <t>Can only be child of `&lt;table&gt;`, `&lt;index&gt;`, or `&lt;tabular&gt;`</t>
         </is>
       </c>
       <c r="E53" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="G53" s="6" t="b">
-        <v>1</v>
+      <c r="G53" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="H53" s="1" t="b">
         <v>0</v>
@@ -2594,32 +2580,32 @@
     <row r="54" ht="17" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>[05] formatting</t>
+          <t>[06] structural</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>`&lt;rtl&gt;`</t>
+          <t>`&lt;corn&gt;`</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Indicates right-to-left direction.</t>
+          <t>Indicates the beginning of a corner cell, typically the top-left header intersection.</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Any context that allows raw text content.</t>
+          <t>Can only be child of `&lt;table&gt;`, `&lt;index&gt;`, or `&lt;tabular&gt;`</t>
         </is>
       </c>
       <c r="E54" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="G54" s="6" t="b">
-        <v>1</v>
+      <c r="G54" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="H54" s="1" t="b">
         <v>0</v>
@@ -2633,12 +2619,12 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>`&lt;fcel&gt;`</t>
+          <t>`&lt;srow&gt;`</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Indicates the beginning of a full / regular cell.</t>
+          <t>Indicates the beginning of a section row header.</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -2667,12 +2653,12 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>`&lt;ecel&gt;`</t>
+          <t>`&lt;lcel&gt;`</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Indicates the beginning of an empty cell.</t>
+          <t>Left-merge extension token; extends the previous cell horizontally (colspan continuation).</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -2701,12 +2687,12 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>`&lt;ched&gt;`</t>
+          <t>`&lt;ucel&gt;`</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Indicates the beginning of a column header cell.</t>
+          <t>Upward-merge extension token; extends the cell above vertically (rowspan continuation)</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -2735,12 +2721,12 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>`&lt;rhed&gt;`</t>
+          <t>`&lt;xcel&gt;`</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Indicates the beginning of a row header cell.</t>
+          <t>Cross/combined span extension token; used where both horizontal and vertical spanning intersect.</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -2769,12 +2755,12 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>`&lt;corn&gt;`</t>
+          <t>`&lt;nl&gt;`</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Indicates the beginning of a corner cell, typically the top-left header intersection.</t>
+          <t>Denotes the end of a table row.</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -2803,21 +2789,21 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>`&lt;srow&gt;`</t>
+          <t>`&lt;ldiv&gt;`</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Indicates the beginning of a section row header.</t>
+          <t>Indicates the beginning of a list item. It can either be empty or contain a `&lt;marker&gt;`.</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Can only be child of `&lt;table&gt;`, `&lt;index&gt;`, or `&lt;tabular&gt;`</t>
+          <t>Can only be child of `&lt;list&gt;`.</t>
         </is>
       </c>
       <c r="E60" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="6" t="b">
         <v>0</v>
@@ -2825,131 +2811,166 @@
       <c r="G60" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="H60" s="1" t="b">
-        <v>0</v>
+      <c r="H60" s="1" t="inlineStr">
+        <is>
+          <t>Only `&lt;marker&gt;`</t>
+        </is>
       </c>
     </row>
     <row r="61" ht="51" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>[06] structural</t>
+          <t>[07] document head</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>`&lt;lcel&gt;`</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>Left-merge extension token; extends the previous cell horizontally (colspan continuation).</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>Can only be child of `&lt;table&gt;`, `&lt;index&gt;`, or `&lt;tabular&gt;`</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="F61" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G61" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="H61" s="1" t="b">
-        <v>0</v>
+          <t>`&lt;title&gt;`</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J61" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="62" ht="34" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>[06] structural</t>
+          <t>[07] document head</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>`&lt;ucel&gt;`</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>Upward-merge extension token; extends the cell above vertically (rowspan continuation)</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>Can only be child of `&lt;table&gt;`, `&lt;index&gt;`, or `&lt;tabular&gt;`</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="F62" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G62" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="H62" s="1" t="b">
-        <v>0</v>
+          <t>`&lt;author&gt;`</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J62" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="63" ht="51" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>[06] structural</t>
+          <t>[07] document head</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>`&lt;xcel&gt;`</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>Cross/combined span extension token; used where both horizontal and vertical spanning intersect.</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>Can only be child of `&lt;table&gt;`, `&lt;index&gt;`, or `&lt;tabular&gt;`</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="F63" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G63" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="H63" s="1" t="b">
-        <v>0</v>
+          <t>`&lt;date&gt;`</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J63" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="64" ht="17" customHeight="1">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>[06] structural</t>
+          <t>[07] document head</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>`&lt;nl&gt;`</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>Denotes the end of a table row.</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>Can only be child of `&lt;table&gt;`, `&lt;index&gt;`, or `&lt;tabular&gt;`</t>
+          <t>`&lt;default_resolution&gt;`</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Defines the default resolution for the document.</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>Can only be child of `&lt;head&gt;`.</t>
         </is>
       </c>
       <c r="E64" s="6" t="b">
@@ -2958,47 +2979,56 @@
       <c r="F64" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="G64" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="H64" s="1" t="b">
+      <c r="G64" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H64" s="6" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="65" ht="34" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>[06] structural</t>
+          <t>[07] document head</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>`&lt;ldiv&gt;`</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>Indicates the beginning of a list item. It can either be empty or contain a `&lt;marker&gt;`.</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>Can only be child of `&lt;list&gt;`.</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="F65" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G65" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="H65" s="1" t="inlineStr">
-        <is>
-          <t>Only `&lt;marker&gt;`</t>
-        </is>
+          <t>`&lt;page_size&gt;`</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J65" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="66" ht="17" customHeight="1">
@@ -3009,7 +3039,7 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>`&lt;title&gt;`</t>
+          <t>`&lt;language&gt;`</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
@@ -3054,7 +3084,7 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>`&lt;author&gt;`</t>
+          <t>`&lt;generated_by&gt;`</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -3099,7 +3129,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>`&lt;date&gt;`</t>
+          <t>`&lt;topic&gt;`</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
@@ -3144,30 +3174,41 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>`&lt;default_resolution&gt;`</t>
+          <t>`&lt;summary&gt;`</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Defines the default resolution for the document.</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Can only be child of `&lt;head&gt;`.</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="F69" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G69" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H69" s="6" t="b">
-        <v>0</v>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J69" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="70" ht="17" customHeight="1">
@@ -3178,7 +3219,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>`&lt;page_size&gt;`</t>
+          <t>`&lt;document_hash&gt;`</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
@@ -3223,7 +3264,7 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>`&lt;language&gt;`</t>
+          <t>`&lt;licenses&gt;`</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
@@ -3268,7 +3309,7 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>`&lt;generated_by&gt;`</t>
+          <t>`&lt;data_classification&gt;`</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
@@ -3313,7 +3354,7 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>`&lt;topic&gt;`</t>
+          <t>`&lt;acceptable_use&gt;`</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
@@ -3358,7 +3399,7 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>`&lt;summary&gt;`</t>
+          <t>`&lt;stewardship&gt;`</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
@@ -3403,7 +3444,7 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>`&lt;document_hash&gt;`</t>
+          <t>`&lt;access_policy&gt;`</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
@@ -3448,7 +3489,7 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>`&lt;licenses&gt;`</t>
+          <t>`&lt;retention_policy&gt;`</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
@@ -3493,7 +3534,7 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>`&lt;data_classification&gt;`</t>
+          <t>`&lt;compliance_requirements&gt;`</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
@@ -3531,239 +3572,400 @@
       </c>
     </row>
     <row r="78" ht="17" customHeight="1">
-      <c r="A78" s="7" t="inlineStr">
-        <is>
-          <t>[07] document head</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>`&lt;acceptable_use&gt;`</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F78" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H78" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="J78" s="1" t="b">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>[01a] semantic (top)</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="inlineStr">
+        <is>
+          <t>`&lt;track&gt;`</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>Captures a time-aligned media transcript (subtitles, captions, or diarized speech). The body may open with a single `&lt;cover&gt;` (a track-wide image), then a sequence of cue blocks, each introduced by a `&lt;bdiv&gt;` delimiter; a non-empty `&lt;track&gt;` body must begin with a `&lt;cover&gt;` or a `&lt;bdiv&gt;`. A cue block carries a mandatory start time, an optional end time (each a run of `&lt;hours&gt;`/`&lt;minutes&gt;`/`&lt;seconds&gt;`/`&lt;msecs&gt;`), an optional `&lt;chapter&gt;`, an optional `&lt;frame&gt;`, an optional `&lt;audio&gt;`, and an optional transcript of `&lt;voice&gt;`-attributed turns.</t>
+        </is>
+      </c>
+      <c r="D78" s="1" t="inlineStr">
+        <is>
+          <t>Any context that allows semantic elements.</t>
+        </is>
+      </c>
+      <c r="E78" t="b">
+        <v>1</v>
+      </c>
+      <c r="F78" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Only within a cue block transcript</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>`&lt;cover&gt;` before the first cue block; within cue blocks, `&lt;chapter&gt;`, `&lt;frame&gt;`, `&lt;audio&gt;`, and `&lt;voice&gt;`</t>
+        </is>
+      </c>
+      <c r="I78" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="79" ht="17" customHeight="1">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>[07] document head</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="inlineStr">
-        <is>
-          <t>`&lt;stewardship&gt;`</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H79" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="J79" s="1" t="b">
-        <v>1</v>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>[01b] semantic (inner)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>`&lt;cover&gt;`</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>A representative image for a `&lt;track&gt;` as a whole — for example podcast artwork, a poster, or a title card. Appears once, before the first cue block. Same shape as `&lt;frame&gt;`: an optional element head followed by an optional `&lt;src&gt;`.</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Can only appear inside a `&lt;track&gt;`, before the first `&lt;bdiv&gt;`.</t>
+        </is>
+      </c>
+      <c r="E79" t="b">
+        <v>1</v>
+      </c>
+      <c r="F79" t="b">
+        <v>1</v>
+      </c>
+      <c r="G79" t="b">
+        <v>0</v>
+      </c>
+      <c r="H79" t="b">
+        <v>1</v>
+      </c>
+      <c r="I79" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="80" ht="17" customHeight="1">
-      <c r="A80" s="7" t="inlineStr">
-        <is>
-          <t>[07] document head</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>`&lt;access_policy&gt;`</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H80" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="J80" s="1" t="b">
-        <v>1</v>
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>[01b] semantic (inner)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>`&lt;frame&gt;`</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>The still image of the recording at a `&lt;track&gt;` cue block's start time. Shaped like `&lt;picture&gt;`: an optional element head followed by an optional `&lt;src&gt;`.</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Can only appear inside a `&lt;track&gt;` cue block.</t>
+        </is>
+      </c>
+      <c r="E80" t="b">
+        <v>1</v>
+      </c>
+      <c r="F80" t="b">
+        <v>1</v>
+      </c>
+      <c r="G80" t="b">
+        <v>0</v>
+      </c>
+      <c r="H80" t="b">
+        <v>1</v>
+      </c>
+      <c r="I80" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="81" ht="17" customHeight="1">
-      <c r="A81" s="7" t="inlineStr">
-        <is>
-          <t>[07] document head</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>`&lt;retention_policy&gt;`</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H81" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="J81" s="1" t="b">
-        <v>1</v>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>[01b] semantic (inner)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>`&lt;audio&gt;`</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>The recording over a `&lt;track&gt;` cue block's interval `[start, end]` — a temporal crop of the track's audio, as a `&lt;picture&gt;` crop corresponds to its page region. Requires the cue block to carry an end time; the timestamps are authoritative and the clip is a best-effort fragment. Same shape as `&lt;frame&gt;`.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Can only appear inside a `&lt;track&gt;` cue block.</t>
+        </is>
+      </c>
+      <c r="E81" t="b">
+        <v>1</v>
+      </c>
+      <c r="F81" t="b">
+        <v>1</v>
+      </c>
+      <c r="G81" t="b">
+        <v>0</v>
+      </c>
+      <c r="H81" t="b">
+        <v>1</v>
+      </c>
+      <c r="I81" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="82" ht="17" customHeight="1">
-      <c r="A82" s="7" t="inlineStr">
-        <is>
-          <t>[07] document head</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>`&lt;compliance_requirements&gt;`</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="J82" s="1" t="b">
-        <v>1</v>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>[01b] semantic (inner)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>`&lt;voice&gt;`</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Speaker attribution for a transcript turn within a `&lt;track&gt;` cue block. Handled like `&lt;text&gt;` (may carry its own element head and inline formatting).</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Can only appear inside a `&lt;track&gt;` cue block.</t>
+        </is>
+      </c>
+      <c r="E82" t="b">
+        <v>1</v>
+      </c>
+      <c r="F82" t="b">
+        <v>1</v>
+      </c>
+      <c r="G82" t="b">
+        <v>1</v>
+      </c>
+      <c r="H82" t="b">
+        <v>1</v>
+      </c>
+      <c r="I82" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n"/>
-      <c r="B83" s="1" t="n"/>
-      <c r="C83" s="1" t="n"/>
-      <c r="D83" s="1" t="n"/>
-      <c r="F83" s="1" t="n"/>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>[01b] semantic (inner)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>`&lt;chapter&gt;`</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>A chapter or section title for a `&lt;track&gt;`. It marks a chapter boundary at the start time of the cue block that carries it; the chapter runs until the next `&lt;chapter&gt;` (or `&lt;/track&gt;`), and the region before the first `&lt;chapter&gt;` is unchaptered. Only the start time matters — the cue block's end time bounds its transcript, not the chapter. Chapters form a flat partition (no nesting, no overlap). Handled like `&lt;text&gt;` (may carry its own element head and inline formatting).</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Can only appear inside a `&lt;track&gt;` cue block, after the start (and optional end) timestamp and before any `&lt;frame&gt;`.</t>
+        </is>
+      </c>
+      <c r="E83" t="b">
+        <v>1</v>
+      </c>
+      <c r="F83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G83" t="b">
+        <v>1</v>
+      </c>
+      <c r="H83" t="b">
+        <v>1</v>
+      </c>
+      <c r="I83" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="n"/>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>[06] structural</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>`&lt;bdiv&gt;`</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Indicates the beginning of a `&lt;track&gt;` cue block.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Can only be a child of `&lt;track&gt;`.</t>
+        </is>
+      </c>
+      <c r="E84" t="b">
+        <v>0</v>
+      </c>
+      <c r="F84" t="b">
+        <v>0</v>
+      </c>
+      <c r="G84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H84" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>[04] payload</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>`&lt;hours&gt;`</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Hours component of a `&lt;track&gt;` cue timestamp. Optional within a timestamp run (defaults to 0).</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Can only be part of a timestamp run in a `&lt;track&gt;` cue block.</t>
+        </is>
+      </c>
+      <c r="E85" t="b">
+        <v>0</v>
+      </c>
+      <c r="F85" t="b">
+        <v>0</v>
+      </c>
+      <c r="G85" t="b">
+        <v>0</v>
+      </c>
+      <c r="H85" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>[04] payload</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>`&lt;minutes&gt;`</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Minutes component of a `&lt;track&gt;` cue timestamp. Optional within a timestamp run (defaults to 0).</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Can only be part of a timestamp run in a `&lt;track&gt;` cue block.</t>
+        </is>
+      </c>
+      <c r="E86" t="b">
+        <v>0</v>
+      </c>
+      <c r="F86" t="b">
+        <v>0</v>
+      </c>
+      <c r="G86" t="b">
+        <v>0</v>
+      </c>
+      <c r="H86" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>[04] payload</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>`&lt;seconds&gt;`</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Seconds component of a `&lt;track&gt;` cue timestamp.</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Can only be part of a timestamp run in a `&lt;track&gt;` cue block.</t>
+        </is>
+      </c>
+      <c r="E87" t="b">
+        <v>0</v>
+      </c>
+      <c r="F87" t="b">
+        <v>0</v>
+      </c>
+      <c r="G87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H87" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>[04] payload</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>`&lt;msecs&gt;`</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Milliseconds component of a `&lt;track&gt;` cue timestamp. Optional within a timestamp run (defaults to 0).</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Can only be part of a timestamp run in a `&lt;track&gt;` cue block.</t>
+        </is>
+      </c>
+      <c r="E88" t="b">
+        <v>0</v>
+      </c>
+      <c r="F88" t="b">
+        <v>0</v>
+      </c>
+      <c r="G88" t="b">
+        <v>0</v>
+      </c>
+      <c r="H88" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H82"/>
@@ -3980,7 +4182,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>`&lt;hour&gt;`</t>
+          <t>`&lt;layer&gt;`</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3990,279 +4192,294 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional; default: "body"</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Non-negative integer</t>
+          <t>{"body", "background", "furniture"}</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>The layer value: "body" is for the document's main content, "background" is for watermarks and other background components, while "furniture" is the fallback for any supplementary components not contributing to the document's main content, such as navigation or decorations.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>`&lt;minute&gt;`</t>
+          <t>`&lt;heading&gt;`</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>`value`</t>
+          <t>`level`</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional; default "1"</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Non-negative integer</t>
+          <t>Positive integer</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>The heading depth (1 = top-level).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>`&lt;second&gt;`</t>
+          <t>`&lt;value&gt;`</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>`value`</t>
+          <t>`class`</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional; default: "read_only"</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Non-negative integer</t>
+          <t>{"read_only", "fillable"}</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>The value type.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>`&lt;centisecond&gt;`</t>
+          <t>`&lt;list&gt;`</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>`value`</t>
+          <t>`class`</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional; default: "unordered"</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Non-negative integer</t>
+          <t>{"unordered", "ordered"}</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>The list type.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>`&lt;layer&gt;`</t>
+          <t>`&lt;picture&gt;`</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>`value`</t>
+          <t>`class`</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Optional; default: "body"</t>
+          <t>Optional; default: "undefined"</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{"body", "background", "furniture"}</t>
+          <t>{"undefined", "chart"}</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>The layer value: "body" is for the document's main content, "background" is for watermarks and other background components, while "furniture" is the fallback for any supplementary components not contributing to the document's main content, such as navigation or decorations.</t>
+          <t>The picture type.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>`&lt;heading&gt;`</t>
+          <t>`&lt;checkbox&gt;`</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>`level`</t>
+          <t>`class`</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Optional; default "1"</t>
+          <t>Optional; default: "unselected"</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Positive integer</t>
+          <t>{"unselected", "selected"}</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>The heading depth (1 = top-level).</t>
+          <t>The checkbox type.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>`&lt;value&gt;`</t>
+          <t>`&lt;label&gt;`</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>`class`</t>
+          <t>`value`</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Optional; default: "read_only"</t>
+          <t>Optional; default: "undefined"</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{"read_only", "fillable"}</t>
+          <t>Different value domains may be recommended per host element (not to be validated).</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>The value type.</t>
+          <t>A label for concretely specifying a subclass type for the host element.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>`&lt;list&gt;`</t>
+          <t>`&lt;thread&gt;`</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>`class`</t>
+          <t>`thread_id`</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Optional; default: "unordered"</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"unordered", "ordered"}</t>
+          <t>Positive integer</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>The list type.</t>
+          <t>The ID of the thread. All `&lt;thread&gt;` elements that share a given `thread_id` must be under the same host element type (e.g. all under `&lt;text&gt;`, not mixed `&lt;text&gt;` and `&lt;picture&gt;`).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>`&lt;picture&gt;`</t>
+          <t>`&lt;h_thread&gt;`</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>`class`</t>
+          <t>`h_thread_id`</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Optional; default: "undefined"</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{"undefined", "chart"}</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>The picture type.</t>
+          <t>Positive integer</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>`&lt;checkbox&gt;`</t>
+          <t>`&lt;xref&gt;`</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>`class`</t>
+          <t>`thread_id`</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Optional; default: "unselected"</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>{"unselected", "selected"}</t>
+          <t>Positive integer</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>The checkbox type.</t>
+          <t>The ID of the referenced thread. This must be defined by at least one `&lt;thread&gt;` in the document.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>`&lt;label&gt;`</t>
+          <t>`&lt;href&gt;`</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>`value`</t>
+          <t>`uri`</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Optional; default: "undefined"</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Different value domains may be recommended per host element (not to be validated).</t>
+          <t>URI</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>A label for concretely specifying a subclass type for the host element.</t>
+          <t>The URI of the referenced resource.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>`&lt;thread&gt;`</t>
+          <t>`&lt;src&gt;`</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>`thread_id`</t>
+          <t>`uri`</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -4272,46 +4489,51 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Positive integer</t>
+          <t>URI</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>The ID of the thread. All `&lt;thread&gt;` elements that share a given `thread_id` must be under the same host element type (e.g. all under `&lt;text&gt;`, not mixed `&lt;text&gt;` and `&lt;picture&gt;`).</t>
+          <t>The source URI. May use a `data:` URI (RFC 2397) with base64-encoded payload, e.g. `uri="data:image/png;base64,…"`. Relative URIs are allowed too, e.g. `uri="assets/chart.svg"`.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>`&lt;h_thread&gt;`</t>
+          <t>`&lt;field_heading&gt;`</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>`h_thread_id`</t>
+          <t>`level`</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional; default "1"</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>Positive integer</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>The field heading depth (1 = top-level).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>`&lt;xref&gt;`</t>
+          <t>`&lt;hours&gt;`</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>`thread_id`</t>
+          <t>`value`</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4321,24 +4543,24 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Positive integer</t>
+          <t>Non-negative integer</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>The ID of the referenced thread. This must be defined by at least one `&lt;thread&gt;` in the document.</t>
+          <t>Hours component of a track cue timestamp.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>`&lt;href&gt;`</t>
+          <t>`&lt;minutes&gt;`</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>`uri`</t>
+          <t>`value`</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4348,24 +4570,24 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>URI</t>
+          <t>Integer within [0, 59]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>The URI of the referenced resource.</t>
+          <t>Minutes component of a track cue timestamp.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>`&lt;src&gt;`</t>
+          <t>`&lt;seconds&gt;`</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>`uri`</t>
+          <t>`value`</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4375,39 +4597,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>URI</t>
+          <t>Integer within [0, 59]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>The source URI. May use a `data:` URI (RFC 2397) with base64-encoded payload, e.g. `uri="data:image/png;base64,…"`. Relative URIs are allowed too, e.g. `uri="assets/chart.svg"`.</t>
+          <t>Seconds component of a track cue timestamp.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>`&lt;field_heading&gt;`</t>
+          <t>`&lt;msecs&gt;`</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>`level`</t>
+          <t>`value`</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Optional; default "1"</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Positive integer</t>
+          <t>Integer within [0, 999]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>The field heading depth (1 = top-level).</t>
+          <t>Milliseconds component of a track cue timestamp.</t>
         </is>
       </c>
     </row>

--- a/reference/input/reference.xlsx
+++ b/reference/input/reference.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>*Semantic elements* capture core components with specific meaning and functional role in the document (e.g. a paragraph, a table, a list etc.) and may optionally begin with a [element head](#element-head).
+          <t>*Semantic elements* capture core document components with specific meaning and functional role (e.g. a paragraph, a table, a list etc.) and may optionally begin with a [element head](#element-head).
 They are generally meant to be interpreted as block-level elements (although they can also be inlined via nesting).
 Semantic elements that can appear on the top level within `&lt;doclang&gt;` are called *primary*, while those that can only appear within other semantic elements are called *secondary*.</t>
         </is>
@@ -766,7 +766,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Indicates a page break. A paginated document may be divided into pages using the `&lt;page_break/&gt;` empty element. Any page content, as split by `&lt;page_break/&gt;`, forms a valid DocLang [document body](#head-and-body-areas), i.e. would be a valid DocLang document if wrapped in a `doclang` root element.</t>
+          <t>Indicates a page break. A paginated document may be divided into pages using the `&lt;page_break/&gt;` empty element. Any page content, as split by `&lt;page_break/&gt;`, forms a valid DocLang [document body](#head-and-body-areas), i.e. would be a valid DocLang instance if wrapped in a `doclang` root element.</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -1516,7 +1516,7 @@
       <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Optional part of the element head for capturing an associated caption. Unlike `&lt;description&gt;` or `&lt;summary&gt;`, `&lt;caption&gt;` is an actual
-document component, which can have its own location information etc. For example, a caption shown underneath a chart.</t>
+document component, which can have its own location information etc. For example, a caption shown underneath a chart. An element head may contain multiple captions, e.g. a figure with both a title above and a note below, or the same caption in several languages.</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>The conceptual layer of the host element in the document.</t>
+          <t>The conceptual layer of the host element in the DocLang instance.</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>Defines the default resolution for the document.</t>
+          <t>Defines the default resolution for the DocLang instance.</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The DocLang specification version the document is supposed to validate against, in "MAJOR.MINOR" format, i.e. first two positions of Semantic Verisoning.</t>
+          <t>The DocLang specification version the DocLang instance is supposed to validate against, in "MAJOR.MINOR" format, i.e. first two positions of Semantic Verisoning.</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>The layer value: "body" is for the document's main content, "background" is for watermarks and other background components, while "furniture" is the fallback for any supplementary components not contributing to the document's main content, such as navigation or decorations.</t>
+          <t>The layer value: "body" is for the main content, "background" is for watermarks and other background components, while "furniture" is the fallback for any supplementary components not contributing to the main content, such as navigation or decorations.</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>The ID of the referenced thread. This must be defined by at least one `&lt;thread&gt;` in the document.</t>
+          <t>The ID of the referenced thread. This must be defined by at least one `&lt;thread&gt;` in the DocLang instance.</t>
         </is>
       </c>
     </row>

--- a/reference/input/reference.xlsx
+++ b/reference/input/reference.xlsx
@@ -800,7 +800,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Represents a piece of cohesive text as that would appear in a paragraph. Note: a special construct related to this element is the so-called "virtual `&lt;text&gt;`", which can occur only as a list item or a table cell — see `&lt;list&gt;` and `&lt;table&gt;` below for details.</t>
+          <t>Represents a piece of cohesive text as that would appear in a paragraph. Note: a special construct related to this element is the so-called "virtual `&lt;text&gt;`", which can occur only as a list item, a table cell or a transcript turn — see [Lists](#lists).</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Captures a list. List items are started by the respective structural elements (`&lt;ldiv&gt;`). A non-empty `&lt;list&gt;` element body must begin with such a structural element. A list item can be defined without a wrapping tag, i.e. as pure (optional) element head followed by raw text; this is called an "virtual `&lt;text&gt;`" and is handled exactly like a regular `&lt;text&gt;` element.</t>
+          <t>Captures a list. List items are started by the respective structural elements (`&lt;ldiv&gt;`). A non-empty `&lt;list&gt;` element body must begin with such a structural element. Each list item can be any semantic element sequence or a virtual `&lt;text&gt;`.</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Captures a table in an OTSL-based format. Table cells are started by the respective structural elements (`&lt;fcel&gt;` etc). A non-empty `&lt;table&gt;` element body must begin with such a structural element. A table cell can be defined without a wrapping tag, i.e. as pure (optional) element head followed by raw text; this is called an "virtual `&lt;text&gt;`" and is handled exactly like a regular `&lt;text&gt;` element.</t>
+          <t>Captures a table in an OTSL-based format. Table cells are started by the respective structural elements (`&lt;fcel&gt;` etc). A non-empty `&lt;table&gt;` element body must begin with such a structural element. Each table cell can be any semantic element sequence or a virtual `&lt;text&gt;`.</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Captures an index, e.g. for a table of contents or glossary, in an OTSL-based format. Index cells are started by the respective structural elements (`&lt;fcel&gt;` etc). A non-empty `&lt;index&gt;` element body must begin with such a structural element. A cell can be defined without a wrapping tag, i.e. as pure (optional) element head followed by raw text; this is called an "virtual `&lt;text&gt;`" and is handled exactly like a regular `&lt;text&gt;` element.</t>
+          <t>Captures an index, e.g. for a table of contents or glossary, in an OTSL-based format. Index cells are started by the respective structural elements (`&lt;fcel&gt;` etc). A non-empty `&lt;index&gt;` element body must begin with such a structural element. Each cell can be any semantic element sequence or a virtual `&lt;text&gt;`.</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>Captures a time-aligned media transcript (subtitles, captions, or diarized speech). The body may open with a single `&lt;cover&gt;` (a track-wide image), then a sequence of cue blocks, each introduced by a `&lt;bdiv&gt;` delimiter; a non-empty `&lt;track&gt;` body must begin with a `&lt;cover&gt;` or a `&lt;bdiv&gt;`. A cue block carries a mandatory start time, an optional end time (each a run of `&lt;hours&gt;`/`&lt;minutes&gt;`/`&lt;seconds&gt;`/`&lt;msecs&gt;`), an optional `&lt;chapter&gt;`, an optional `&lt;frame&gt;`, an optional `&lt;audio&gt;`, and an optional transcript of `&lt;voice&gt;`-attributed turns.</t>
+          <t>Captures a time-aligned media transcript (subtitles, captions, or diarized speech). The body may open with a single `&lt;cover&gt;` (a track-wide image), then a sequence of cue blocks, each introduced by a `&lt;bdiv&gt;` delimiter; a non-empty `&lt;track&gt;` body must begin with a `&lt;cover&gt;` or a `&lt;bdiv&gt;`. A cue block carries a mandatory start time, an optional end time (each a run of `&lt;hours&gt;`/`&lt;minutes&gt;`/`&lt;seconds&gt;`/`&lt;msecs&gt;`), an optional `&lt;chapter&gt;`, an optional `&lt;frame&gt;`, an optional `&lt;audio&gt;`, and an optional transcript of turns, each an optional `&lt;voice&gt;` followed by its content, which can be any semantic element sequence or a virtual `&lt;text&gt;`.</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
@@ -3595,17 +3595,19 @@
       <c r="E78" t="b">
         <v>1</v>
       </c>
-      <c r="F78" s="1" t="b">
-        <v>1</v>
+      <c r="F78" s="1" t="inlineStr">
+        <is>
+          <t>TRUE, also on transcript turn level in case of virtual `&lt;text&gt;`</t>
+        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Only within a cue block transcript</t>
+          <t>Only on transcript turn level, in case of virtual `&lt;text&gt;`</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>`&lt;cover&gt;` before the first cue block; within cue blocks, `&lt;chapter&gt;`, `&lt;frame&gt;`, `&lt;audio&gt;`, and `&lt;voice&gt;`</t>
+          <t>`&lt;cover&gt;` before the first cue block; within cue blocks, `&lt;chapter&gt;`, `&lt;frame&gt;`, `&lt;audio&gt;` and `&lt;voice&gt;`; on transcript turn level, any</t>
         </is>
       </c>
       <c r="I78" t="b">

--- a/reference/input/reference.xlsx
+++ b/reference/input/reference.xlsx
@@ -544,7 +544,7 @@
       <c r="B3" s="8" t="inlineStr">
         <is>
           <t>*Semantic elements* capture core document components with specific meaning and functional role (e.g. a paragraph, a table, a list etc.) and may optionally begin with a [element head](#element-head).
-They are generally meant to be interpreted as block-level elements (although they can also be inlined via nesting).
+They are generally meant to be read as separate blocks, such as a paragraph, although some can also be nested within text.
 Semantic elements that can appear on the top level within `&lt;doclang&gt;` are called *primary*, while those that can only appear within other semantic elements are called *secondary*.</t>
         </is>
       </c>
@@ -800,7 +800,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Represents a piece of cohesive text as that would appear in a paragraph. Note: a special construct related to this element is the so-called "virtual `&lt;text&gt;`", which can occur only as a list item or a table cell — see `&lt;list&gt;` and `&lt;table&gt;` below for details.</t>
+          <t>Represents a piece of cohesive text as that would appear in a paragraph. A list item, or a cell of a `&lt;table&gt;`, `&lt;index&gt;` or `&lt;tabular&gt;`, may also consist of raw text, optionally preceded by an element head, without wrapping `&lt;text&gt;` tags. Such content is called a *virtual `&lt;text&gt;`* and is interpreted exactly as if it were wrapped in `&lt;text&gt;` tags.</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Captures a list. List items are started by the respective structural elements (`&lt;ldiv&gt;`). A non-empty `&lt;list&gt;` element body must begin with such a structural element. A list item can be defined without a wrapping tag, i.e. as pure (optional) element head followed by raw text; this is called an "virtual `&lt;text&gt;`" and is handled exactly like a regular `&lt;text&gt;` element.</t>
+          <t>Captures a list. List items are started by the respective structural elements (`&lt;ldiv&gt;`). A non-empty `&lt;list&gt;` element body must begin with such a structural element. A list item can be any semantic element sequence or a virtual `&lt;text&gt;`.</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Captures a table in an OTSL-based format. Table cells are started by the respective structural elements (`&lt;fcel&gt;` etc). A non-empty `&lt;table&gt;` element body must begin with such a structural element. A table cell can be defined without a wrapping tag, i.e. as pure (optional) element head followed by raw text; this is called an "virtual `&lt;text&gt;`" and is handled exactly like a regular `&lt;text&gt;` element.</t>
+          <t>Captures a table in an OTSL-based format. Table cells are started by the respective structural elements (`&lt;fcel&gt;` etc). A non-empty `&lt;table&gt;` element body must begin with such a structural element. A table cell can be any semantic element sequence or a virtual `&lt;text&gt;`.</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Captures an index, e.g. for a table of contents or glossary, in an OTSL-based format. Index cells are started by the respective structural elements (`&lt;fcel&gt;` etc). A non-empty `&lt;index&gt;` element body must begin with such a structural element. A cell can be defined without a wrapping tag, i.e. as pure (optional) element head followed by raw text; this is called an "virtual `&lt;text&gt;`" and is handled exactly like a regular `&lt;text&gt;` element.</t>
+          <t>Captures an index, e.g. for a table of contents or glossary, in an OTSL-based format. Index cells are started by the respective structural elements (`&lt;fcel&gt;` etc). A non-empty `&lt;index&gt;` element body must begin with such a structural element. A cell can be any semantic element sequence or a virtual `&lt;text&gt;`.</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
